--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run6/epoch_60/per_file_predictions_epoch_60.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run6/epoch_60/per_file_predictions_epoch_60.xlsx
@@ -808,706 +808,706 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9969,0.0003,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.0001,0.0000,0.9995</t>
-  </si>
-  <si>
-    <t>0.9843,0.0009,0.0006,0.0056</t>
-  </si>
-  <si>
-    <t>0.0758,0.0023,0.0027,0.9502</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.9956,0.0003,0.0023,0.0001</t>
+  </si>
+  <si>
+    <t>0.0018,0.0001,0.0007,0.9985</t>
+  </si>
+  <si>
+    <t>0.9708,0.0015,0.0010,0.0171</t>
+  </si>
+  <si>
+    <t>0.1758,0.0008,0.0003,0.8952</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0002</t>
   </si>
   <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0001</t>
+    <t>0.9995,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0883,0.0020,0.8984,0.0001</t>
+  </si>
+  <si>
+    <t>0.0018,0.0004,0.9977,0.0000</t>
+  </si>
+  <si>
+    <t>0.5212,0.0003,0.6682,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0006,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.8873,0.0001,0.2489,0.0000</t>
+  </si>
+  <si>
+    <t>0.0032,0.9905,0.0137,0.0007</t>
+  </si>
+  <si>
+    <t>0.0002,0.9995,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0042,0.9947,0.0013,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9983,0.0016,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.6475,0.0004,0.4105,0.0002</t>
+  </si>
+  <si>
+    <t>0.8711,0.0015,0.0852,0.0008</t>
+  </si>
+  <si>
+    <t>0.0007,0.0001,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0180,0.0008,0.9760,0.0006</t>
+  </si>
+  <si>
+    <t>0.0538,0.0000,0.9718,0.0000</t>
+  </si>
+  <si>
+    <t>0.0905,0.0002,0.9485,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9995,0.0005</t>
+  </si>
+  <si>
+    <t>0.1052,0.9260,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.1243,0.8433,0.0148,0.0007</t>
+  </si>
+  <si>
+    <t>0.0002,0.0076,0.9993,0.0023</t>
+  </si>
+  <si>
+    <t>0.0002,0.9997,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9969,0.0002,0.0023,0.0001</t>
+  </si>
+  <si>
+    <t>0.0054,0.0077,0.9880,0.0029</t>
+  </si>
+  <si>
+    <t>0.0597,0.9425,0.0037,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.9992,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0026,0.9836,0.0351,0.0002</t>
+  </si>
+  <si>
+    <t>0.0011,0.0005,0.9967,0.0005</t>
+  </si>
+  <si>
+    <t>0.0010,0.0069,0.9947,0.0014</t>
+  </si>
+  <si>
+    <t>0.0028,0.0003,0.9938,0.0005</t>
+  </si>
+  <si>
+    <t>0.0002,0.0591,0.9981,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0044,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.7799,0.0144,0.0016,0.0724</t>
+  </si>
+  <si>
+    <t>0.0008,0.9992,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0656,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0286,0.9959,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9996,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0009,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0044,0.9981,0.0003</t>
+  </si>
+  <si>
+    <t>0.9985,0.0008,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0008,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0012,0.9998,0.0009</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9961,0.0036,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9958,0.8893,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0932,0.9994,0.0002</t>
+  </si>
+  <si>
+    <t>0.0018,0.0017,0.9942,0.0012</t>
+  </si>
+  <si>
+    <t>0.0000,0.9958,0.9984,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0057,0.9941,0.0018,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9887,0.0002,0.0166,0.0000</t>
+  </si>
+  <si>
+    <t>0.8950,0.0025,0.1177,0.0001</t>
+  </si>
+  <si>
+    <t>0.0020,0.0003,0.9983,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9979,0.0695,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9835,0.9709,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0321,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0129,0.9982</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.0000,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0032,0.0001,0.0007,0.9978</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.0003,0.9997</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9893,0.8212,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9990,0.9968,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9927,0.9559,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.4991,0.8105,0.0009</t>
+  </si>
+  <si>
+    <t>0.0000,0.9967,0.9902,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9867,0.9831,0.0000</t>
+  </si>
+  <si>
+    <t>0.9959,0.0062,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9971,0.0016,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9996,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0008,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9910,0.0118,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.9994,0.0002</t>
+  </si>
+  <si>
+    <t>0.1753,0.0016,0.8783,0.0001</t>
+  </si>
+  <si>
+    <t>0.6685,0.0002,0.3489,0.0010</t>
+  </si>
+  <si>
+    <t>0.0012,0.0003,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9997,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0024,0.9963,0.0018,0.0000</t>
+  </si>
+  <si>
+    <t>0.0024,0.9964,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.7782,0.3050,0.0016,0.0000</t>
+  </si>
+  <si>
+    <t>0.7110,0.0077,0.1653,0.0008</t>
+  </si>
+  <si>
+    <t>0.8585,0.0003,0.2413,0.0000</t>
+  </si>
+  <si>
+    <t>0.0184,0.2863,0.4460,0.0055</t>
+  </si>
+  <si>
+    <t>0.0808,0.0066,0.8461,0.0024</t>
+  </si>
+  <si>
+    <t>0.0015,0.0040,0.0042,0.9942</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0046,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9994,0.9682,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9993,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.1124,0.8212,0.0180,0.0000</t>
+  </si>
+  <si>
+    <t>0.2538,0.7722,0.0016,0.0002</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0004,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9896,0.9976,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0775,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0076,0.9972,0.0001</t>
+  </si>
+  <si>
+    <t>0.0042,0.0027,0.9933,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9623,0.0004,0.0319,0.0002</t>
+  </si>
+  <si>
+    <t>0.6552,0.0000,0.5045,0.0000</t>
+  </si>
+  <si>
+    <t>0.9550,0.0002,0.0331,0.0002</t>
+  </si>
+  <si>
+    <t>0.1470,0.0000,0.0004,0.9166</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.0003,0.9996</t>
+  </si>
+  <si>
+    <t>0.0000,0.9993,0.9689,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0023,0.9949,0.0017,0.0006</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0149,0.9818,0.0026,0.0002</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.5262,0.0000,0.0012,0.6550</t>
+  </si>
+  <si>
+    <t>0.0001,0.0068,0.9987,0.0086</t>
+  </si>
+  <si>
+    <t>0.9902,0.0000,0.0054,0.0008</t>
+  </si>
+  <si>
+    <t>0.1733,0.8796,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.9968,0.0015,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9975,0.0005,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.1530,0.4416,0.1190,0.0002</t>
+  </si>
+  <si>
+    <t>0.9978,0.0005,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9737,0.0263,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9974,0.0007,0.0003,0.0017</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9988,0.0010,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0007,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9938,0.0021,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.7599,0.2282,0.0051,0.0004</t>
+  </si>
+  <si>
+    <t>0.9942,0.0073,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0149,0.0205,0.9653,0.0002</t>
+  </si>
+  <si>
+    <t>0.9998,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9945,0.0026,0.0014,0.0013</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.6112,0.4381,0.0018,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,0.0009,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9892,0.0102,0.0015,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0070,0.9988,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0093,0.9988,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0006,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,1.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.0032,0.0003,0.9952,0.0001</t>
+  </si>
+  <si>
+    <t>0.0144,0.0026,0.9832,0.0002</t>
+  </si>
+  <si>
+    <t>0.0065,0.0029,0.9885,0.0001</t>
+  </si>
+  <si>
+    <t>0.0121,0.0191,0.9751,0.0001</t>
+  </si>
+  <si>
+    <t>0.0043,0.0630,0.9745,0.0001</t>
+  </si>
+  <si>
+    <t>0.0564,0.0007,0.9472,0.0001</t>
+  </si>
+  <si>
+    <t>0.7801,0.0025,0.2017,0.0003</t>
+  </si>
+  <si>
+    <t>0.0135,0.0008,0.9797,0.0004</t>
+  </si>
+  <si>
+    <t>0.5429,0.5986,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0577,0.9666,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9960,0.0063,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.6949,0.4267,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.0524,0.9567,0.0016,0.0001</t>
+  </si>
+  <si>
+    <t>0.9226,0.0277,0.0046,0.0007</t>
+  </si>
+  <si>
+    <t>0.9965,0.0000,0.0015,0.0000</t>
+  </si>
+  <si>
+    <t>0.9875,0.0002,0.0035,0.0002</t>
+  </si>
+  <si>
+    <t>0.4990,0.0036,0.3983,0.0011</t>
+  </si>
+  <si>
+    <t>0.0079,0.0018,0.9856,0.0015</t>
+  </si>
+  <si>
+    <t>0.0032,0.0076,0.9873,0.0011</t>
+  </si>
+  <si>
+    <t>0.1664,0.0239,0.7817,0.0004</t>
+  </si>
+  <si>
+    <t>0.0037,0.0014,0.9946,0.0001</t>
+  </si>
+  <si>
+    <t>0.0169,0.0246,0.9357,0.0006</t>
+  </si>
+  <si>
+    <t>0.9970,0.0018,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9938,0.0037,0.0012,0.0007</t>
+  </si>
+  <si>
+    <t>0.8730,0.0891,0.0157,0.0010</t>
+  </si>
+  <si>
+    <t>0.9983,0.0011,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9982,0.0009,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9985,0.0011,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0007,0.9999,0.0006</t>
+  </si>
+  <si>
+    <t>0.1459,0.2580,0.2443,0.0007</t>
+  </si>
+  <si>
+    <t>0.9786,0.0010,0.0094,0.0014</t>
+  </si>
+  <si>
+    <t>0.0062,0.0000,0.9961,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0008,0.9976,0.0005</t>
+  </si>
+  <si>
+    <t>0.0006,0.0573,0.9946,0.0006</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0263,0.0004,0.9785,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0004,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0079,0.9977,0.0002</t>
+  </si>
+  <si>
+    <t>0.1482,0.0184,0.7095,0.0011</t>
+  </si>
+  <si>
+    <t>0.9979,0.0000,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.9924,0.0000,0.0032,0.0001</t>
   </si>
   <si>
     <t>0.9995,0.0004,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9955,0.0056,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9671,0.0001,0.0395,0.0000</t>
-  </si>
-  <si>
-    <t>0.0144,0.0030,0.9791,0.0002</t>
-  </si>
-  <si>
-    <t>0.0282,0.0002,0.9815,0.0000</t>
-  </si>
-  <si>
-    <t>0.0029,0.0009,0.9951,0.0002</t>
-  </si>
-  <si>
-    <t>0.9920,0.0001,0.0088,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9992,0.0040,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0681,0.9545,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0058,0.9924,0.0019,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.8143,0.0019,0.1888,0.0001</t>
-  </si>
-  <si>
-    <t>0.4817,0.0020,0.5382,0.0002</t>
-  </si>
-  <si>
-    <t>0.0007,0.0001,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0016,0.0001,0.9975,0.0001</t>
-  </si>
-  <si>
-    <t>0.3175,0.0000,0.8365,0.0000</t>
-  </si>
-  <si>
-    <t>0.9784,0.0001,0.0338,0.0000</t>
-  </si>
-  <si>
-    <t>0.0020,0.0003,0.9966,0.0005</t>
-  </si>
-  <si>
-    <t>0.3185,0.7144,0.0016,0.0003</t>
-  </si>
-  <si>
-    <t>0.8781,0.0446,0.0266,0.0010</t>
-  </si>
-  <si>
-    <t>0.0001,0.0097,0.9996,0.0018</t>
-  </si>
-  <si>
-    <t>0.0012,0.9983,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9976,0.0007,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.0443,0.0007,0.9636,0.0007</t>
-  </si>
-  <si>
-    <t>0.0421,0.9585,0.0052,0.0001</t>
-  </si>
-  <si>
-    <t>0.0019,0.9938,0.0273,0.0002</t>
-  </si>
-  <si>
-    <t>0.0166,0.5745,0.3996,0.0007</t>
-  </si>
-  <si>
-    <t>0.0015,0.0009,0.9954,0.0004</t>
-  </si>
-  <si>
-    <t>0.0065,0.0062,0.9821,0.0005</t>
-  </si>
-  <si>
-    <t>0.0188,0.0011,0.9714,0.0011</t>
-  </si>
-  <si>
-    <t>0.0000,0.4502,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.9982,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0007,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.1035,0.5134,0.0040,0.2954</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.5683,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0222,0.9956,0.0001</t>
-  </si>
-  <si>
-    <t>0.0017,0.0000,0.9975,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0004,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0347,0.9976,0.0013</t>
-  </si>
-  <si>
-    <t>0.9677,0.0358,0.0026,0.0001</t>
-  </si>
-  <si>
-    <t>0.9976,0.0009,0.0011,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0035,0.9989,0.0018</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0004,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0007,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9991,0.9782,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0219,0.9976,0.0004</t>
-  </si>
-  <si>
-    <t>0.0016,0.0006,0.9950,0.0009</t>
-  </si>
-  <si>
-    <t>0.0000,0.9990,0.9970,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0093,0.9907,0.0019,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.8086,0.0000,0.3816,0.0000</t>
-  </si>
-  <si>
-    <t>0.9741,0.0130,0.0025,0.0002</t>
-  </si>
-  <si>
-    <t>0.0103,0.0002,0.9933,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.7118,0.9914,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9160,0.9085,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0015,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9965,0.0897,0.0002</t>
-  </si>
-  <si>
-    <t>0.0007,0.0000,0.0017,0.9987</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0026,0.0005,0.0061,0.9948</t>
-  </si>
-  <si>
-    <t>0.0046,0.0001,0.0001,0.9982</t>
-  </si>
-  <si>
-    <t>0.0004,0.0005,0.0006,0.9993</t>
-  </si>
-  <si>
-    <t>0.0001,0.9949,0.1570,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9960,0.9960,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9980,0.9774,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.1825,0.9910,0.0007</t>
-  </si>
-  <si>
-    <t>0.0000,0.9969,0.9870,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9891,0.3617,0.0001</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0018,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0008,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9977,0.0021,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0006,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9960,0.0056,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.0257,0.0195,0.9507,0.0005</t>
-  </si>
-  <si>
-    <t>0.3703,0.0003,0.5997,0.0039</t>
-  </si>
-  <si>
-    <t>0.0101,0.0002,0.9937,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0027,0.9954,0.0038,0.0001</t>
-  </si>
-  <si>
-    <t>0.0016,0.9964,0.0051,0.0001</t>
-  </si>
-  <si>
-    <t>0.8679,0.2243,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0735,0.0017,0.9120,0.0028</t>
-  </si>
-  <si>
-    <t>0.0224,0.0018,0.9677,0.0005</t>
-  </si>
-  <si>
-    <t>0.6570,0.0069,0.2536,0.0003</t>
-  </si>
-  <si>
-    <t>0.9440,0.0062,0.0191,0.0006</t>
-  </si>
-  <si>
-    <t>0.0003,0.0517,0.0006,0.9978</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.9970,0.9390,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9995,0.0014,0.0000</t>
-  </si>
-  <si>
-    <t>0.5417,0.2470,0.0417,0.0001</t>
-  </si>
-  <si>
-    <t>0.0720,0.9352,0.0026,0.0002</t>
-  </si>
-  <si>
-    <t>0.9967,0.0016,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9984,0.0005,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9731,0.9972,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.1359,0.9980,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0010,0.9987,0.0000</t>
-  </si>
-  <si>
-    <t>0.0014,0.0012,0.9973,0.0000</t>
-  </si>
-  <si>
-    <t>0.9951,0.0000,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9715,0.0001,0.0284,0.0001</t>
-  </si>
-  <si>
-    <t>0.0330,0.0000,0.9773,0.0001</t>
-  </si>
-  <si>
-    <t>0.0842,0.0005,0.9214,0.0002</t>
-  </si>
-  <si>
-    <t>0.1705,0.0002,0.0024,0.8548</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0001,0.9998</t>
-  </si>
-  <si>
-    <t>0.0000,0.9987,0.9171,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0004,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9989,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.3113,0.7378,0.0014,0.0003</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9166,0.0004,0.0279,0.0194</t>
-  </si>
-  <si>
-    <t>0.0003,0.0022,0.9981,0.0084</t>
-  </si>
-  <si>
-    <t>0.9939,0.0000,0.0096,0.0001</t>
-  </si>
-  <si>
-    <t>0.1036,0.7997,0.0482,0.0003</t>
-  </si>
-  <si>
-    <t>0.9975,0.0004,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9881,0.0017,0.0069,0.0001</t>
-  </si>
-  <si>
-    <t>0.0703,0.3019,0.2795,0.0001</t>
-  </si>
-  <si>
-    <t>0.9969,0.0005,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.9917,0.0024,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9972,0.0015,0.0004,0.0007</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9986,0.0010,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0004,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9825,0.0023,0.0000,0.0022</t>
-  </si>
-  <si>
-    <t>0.8711,0.1269,0.0025,0.0003</t>
-  </si>
-  <si>
-    <t>0.9562,0.0654,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.6300,0.0098,0.3233,0.0006</t>
-  </si>
-  <si>
-    <t>0.9991,0.0009,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9923,0.0042,0.0018,0.0013</t>
-  </si>
-  <si>
-    <t>0.9989,0.0008,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9935,0.0071,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0008,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9908,0.0039,0.0033,0.0015</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0435,0.9987,0.0003</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.7363,0.9983,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0016,0.0014,0.9948,0.0007</t>
-  </si>
-  <si>
-    <t>0.0113,0.0004,0.9897,0.0001</t>
-  </si>
-  <si>
-    <t>0.0606,0.0010,0.9439,0.0001</t>
-  </si>
-  <si>
-    <t>0.5355,0.0114,0.3834,0.0001</t>
-  </si>
-  <si>
-    <t>0.0248,0.0016,0.9757,0.0000</t>
-  </si>
-  <si>
-    <t>0.7586,0.0008,0.2961,0.0000</t>
-  </si>
-  <si>
-    <t>0.9644,0.0004,0.0238,0.0002</t>
-  </si>
-  <si>
-    <t>0.0027,0.0005,0.9949,0.0003</t>
-  </si>
-  <si>
-    <t>0.0089,0.9922,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.0392,0.9749,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9828,0.0337,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0906,0.9356,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0252,0.9756,0.0025,0.0000</t>
-  </si>
-  <si>
-    <t>0.3353,0.4607,0.0282,0.0011</t>
-  </si>
-  <si>
-    <t>0.9969,0.0000,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.9942,0.0002,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.1763,0.0054,0.7686,0.0024</t>
-  </si>
-  <si>
-    <t>0.0184,0.0038,0.9690,0.0038</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9992,0.0005</t>
-  </si>
-  <si>
-    <t>0.0008,0.0179,0.9941,0.0027</t>
-  </si>
-  <si>
-    <t>0.0102,0.0152,0.9821,0.0004</t>
-  </si>
-  <si>
-    <t>0.0010,0.0004,0.9982,0.0001</t>
-  </si>
-  <si>
-    <t>0.0084,0.9554,0.0241,0.0010</t>
-  </si>
-  <si>
-    <t>0.9970,0.0017,0.0006,0.0006</t>
-  </si>
-  <si>
-    <t>0.9977,0.0006,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.9993,0.0004,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9987,0.0008,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9940,0.0041,0.0015,0.0007</t>
-  </si>
-  <si>
-    <t>0.9949,0.0061,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9998,0.0004</t>
-  </si>
-  <si>
-    <t>0.0253,0.0497,0.8991,0.0019</t>
-  </si>
-  <si>
-    <t>0.9889,0.0004,0.0085,0.0003</t>
-  </si>
-  <si>
-    <t>0.1437,0.0000,0.9431,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0150,0.9972,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.0841,0.9929,0.0007</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0034,0.0011,0.9926,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0009,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0026,0.9977,0.0002</t>
-  </si>
-  <si>
-    <t>0.7631,0.0004,0.2497,0.0003</t>
-  </si>
-  <si>
-    <t>0.9974,0.0000,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.9952,0.0001,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0011,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9985,0.0014,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9985,0.0010,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9962,0.0027,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0003,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9984,0.0014,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0046,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0009,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0025,0.9976,0.0001</t>
-  </si>
-  <si>
-    <t>0.0133,0.0413,0.9228,0.0012</t>
-  </si>
-  <si>
-    <t>0.0047,0.0001,0.9947,0.0002</t>
-  </si>
-  <si>
-    <t>0.0059,0.0026,0.9786,0.0158</t>
-  </si>
-  <si>
-    <t>0.0070,0.0007,0.9885,0.0004</t>
-  </si>
-  <si>
-    <t>0.0021,0.0013,0.9931,0.0021</t>
-  </si>
-  <si>
-    <t>0.9932,0.0000,0.0019,0.0009</t>
-  </si>
-  <si>
-    <t>0.0012,0.0018,0.0001,0.9989</t>
-  </si>
-  <si>
-    <t>0.0289,0.0000,0.0017,0.9791</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.9985,0.0000,0.0001,0.0002</t>
+    <t>0.9996,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0005,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0007,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9972,0.0032,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0079,0.9982,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0006,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0980,0.9977,0.0000</t>
+  </si>
+  <si>
+    <t>0.0152,0.0360,0.9482,0.0005</t>
+  </si>
+  <si>
+    <t>0.0291,0.0000,0.9796,0.0000</t>
+  </si>
+  <si>
+    <t>0.0062,0.0015,0.9848,0.0025</t>
+  </si>
+  <si>
+    <t>0.0005,0.0011,0.9984,0.0002</t>
+  </si>
+  <si>
+    <t>0.0355,0.0002,0.9608,0.0008</t>
+  </si>
+  <si>
+    <t>0.9969,0.0000,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.0010,0.0019,0.0001,0.9992</t>
+  </si>
+  <si>
+    <t>0.0204,0.0001,0.0015,0.9868</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.9927,0.0001,0.0005,0.0013</t>
   </si>
 </sst>
 </file>
@@ -1893,7 +1893,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1907,7 +1907,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1921,7 +1921,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1935,7 +1935,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1949,7 +1949,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1963,7 +1963,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1977,7 +1977,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1991,7 +1991,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2005,7 +2005,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2019,7 +2019,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2033,7 +2033,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2047,7 +2047,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2058,10 +2058,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D14" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2075,7 +2075,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2086,10 +2086,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D16" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2103,7 +2103,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2117,7 +2117,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2131,7 +2131,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2145,7 +2145,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2159,7 +2159,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2173,7 +2173,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2187,7 +2187,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2201,7 +2201,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2212,10 +2212,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2229,7 +2229,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2243,7 +2243,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2257,7 +2257,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2268,10 +2268,10 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2285,7 +2285,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2299,7 +2299,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2310,10 +2310,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D32" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2327,7 +2327,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2341,7 +2341,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2355,7 +2355,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2369,7 +2369,7 @@
         <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2383,7 +2383,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2397,7 +2397,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2411,7 +2411,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2425,7 +2425,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2439,7 +2439,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2453,7 +2453,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2467,7 +2467,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2481,7 +2481,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2495,7 +2495,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2506,10 +2506,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D46" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2523,7 +2523,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2537,7 +2537,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2551,7 +2551,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2562,10 +2562,10 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2579,7 +2579,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2593,7 +2593,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2607,7 +2607,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2621,7 +2621,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2635,7 +2635,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2649,7 +2649,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2663,7 +2663,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2677,7 +2677,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2691,7 +2691,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2705,7 +2705,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2719,7 +2719,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2733,7 +2733,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2747,7 +2747,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2761,7 +2761,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2775,7 +2775,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2789,7 +2789,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2803,7 +2803,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2817,7 +2817,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2831,7 +2831,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2845,7 +2845,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2859,7 +2859,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2873,7 +2873,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2884,10 +2884,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D73" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2901,7 +2901,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2915,7 +2915,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2929,7 +2929,7 @@
         <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2943,7 +2943,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2957,7 +2957,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2971,7 +2971,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2985,7 +2985,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2999,7 +2999,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3013,7 +3013,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3024,10 +3024,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3041,7 +3041,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3055,7 +3055,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3069,7 +3069,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3083,7 +3083,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3094,10 +3094,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3111,7 +3111,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3125,7 +3125,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>349</v>
+        <v>273</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3139,7 +3139,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3153,7 +3153,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3167,7 +3167,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>352</v>
+        <v>278</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3181,7 +3181,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3195,7 +3195,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3209,7 +3209,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3223,7 +3223,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>356</v>
+        <v>272</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3237,7 +3237,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3251,7 +3251,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3265,7 +3265,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3279,7 +3279,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>357</v>
+        <v>272</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3293,7 +3293,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>356</v>
+        <v>278</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3307,7 +3307,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3321,7 +3321,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3335,7 +3335,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3349,7 +3349,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3360,10 +3360,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3377,7 +3377,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3391,7 +3391,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3405,7 +3405,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>280</v>
+        <v>365</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3419,7 +3419,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3433,7 +3433,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3447,7 +3447,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>280</v>
+        <v>368</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3461,7 +3461,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>280</v>
+        <v>368</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3475,7 +3475,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3486,10 +3486,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3500,10 +3500,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3514,10 +3514,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D118" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3528,10 +3528,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3545,7 +3545,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3559,7 +3559,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3573,7 +3573,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3587,7 +3587,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3601,7 +3601,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3615,7 +3615,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3626,10 +3626,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3643,7 +3643,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3657,7 +3657,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3671,7 +3671,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3685,7 +3685,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>318</v>
+        <v>383</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3699,7 +3699,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3713,7 +3713,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3727,7 +3727,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>269</v>
+        <v>386</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3741,7 +3741,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3755,7 +3755,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3769,7 +3769,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3783,7 +3783,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3797,7 +3797,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3811,7 +3811,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3825,7 +3825,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3839,7 +3839,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3850,10 +3850,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D142" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3864,10 +3864,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3881,7 +3881,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3895,7 +3895,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3909,7 +3909,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3923,7 +3923,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3937,7 +3937,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3951,7 +3951,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3965,7 +3965,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3979,7 +3979,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>269</v>
+        <v>403</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3993,7 +3993,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4007,7 +4007,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4018,10 +4018,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D154" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4035,7 +4035,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4049,7 +4049,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4063,7 +4063,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4077,7 +4077,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4091,7 +4091,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4105,7 +4105,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4119,7 +4119,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4130,10 +4130,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D162" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4147,7 +4147,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4161,7 +4161,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4175,7 +4175,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4189,7 +4189,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>411</v>
+        <v>383</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4203,7 +4203,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>412</v>
+        <v>272</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4217,7 +4217,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4231,7 +4231,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>270</v>
+        <v>383</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4245,7 +4245,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4259,7 +4259,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4273,7 +4273,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>320</v>
+        <v>419</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4287,7 +4287,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4301,7 +4301,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4315,7 +4315,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4326,10 +4326,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4343,7 +4343,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4357,7 +4357,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4371,7 +4371,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4385,7 +4385,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4399,7 +4399,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4413,7 +4413,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4427,7 +4427,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4441,7 +4441,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4455,7 +4455,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4466,10 +4466,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4483,7 +4483,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4497,7 +4497,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4511,7 +4511,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4525,7 +4525,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4539,7 +4539,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4553,7 +4553,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4564,10 +4564,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4581,7 +4581,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4592,10 +4592,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4609,7 +4609,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4623,7 +4623,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4634,10 +4634,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D198" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4651,7 +4651,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4665,7 +4665,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4676,10 +4676,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4693,7 +4693,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4707,7 +4707,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4721,7 +4721,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4735,7 +4735,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4746,10 +4746,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D206" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4763,7 +4763,7 @@
         <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4777,7 +4777,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>451</v>
+        <v>432</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4791,7 +4791,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4805,7 +4805,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4819,7 +4819,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4830,10 +4830,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4847,7 +4847,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4861,7 +4861,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4875,7 +4875,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4889,7 +4889,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4903,7 +4903,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4917,7 +4917,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4931,7 +4931,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4945,7 +4945,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4959,7 +4959,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4970,10 +4970,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D222" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4987,7 +4987,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5001,7 +5001,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5015,7 +5015,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5029,7 +5029,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5043,7 +5043,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5057,7 +5057,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5071,7 +5071,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5085,7 +5085,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5099,7 +5099,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5110,10 +5110,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5127,7 +5127,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5141,7 +5141,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5155,7 +5155,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5169,7 +5169,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5183,7 +5183,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>479</v>
+        <v>272</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5197,7 +5197,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5211,7 +5211,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5225,7 +5225,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>482</v>
+        <v>327</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5239,7 +5239,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5253,7 +5253,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>484</v>
+        <v>277</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5435,7 +5435,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="256" spans="1:4">
